--- a/sheets/민요/검수/물레타령.xlsx
+++ b/sheets/민요/검수/물레타령.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,48 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2607,8 +2729,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -2627,730 +2753,657 @@
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">물레타령 — 민요채보-1/물레타령.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">물레타령</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+      <c s="8" r="P2"/>
+      <c s="8" r="Q2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">정</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢南</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">우리</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">우리</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">님</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南姑</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">우리</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑姑</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">위리</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑姑</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">병</t>
         </is>
       </c>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3" t="inlineStr">
+      <c r="P3" s="15"/>
+      <c r="Q3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">물레야</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="14"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="M4" s="18"/>
+      <c r="N4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O4" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">빙</t>
         </is>
       </c>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="P4" s="14"/>
+      <c r="Q4" s="18"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">실도</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">뒷</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">실도</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢南</t>
         </is>
       </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="I5" s="20"/>
+      <c r="J5" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="K5" s="20"/>
+      <c r="L5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="M5" s="20"/>
+      <c r="N5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">빙</t>
         </is>
       </c>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="P5" s="14"/>
+      <c r="Q5" s="20"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑南</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">님</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑姑</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">무명</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑姑</t>
         </is>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G6" s="16"/>
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑姑</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">매의위에나</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑姑</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">한송이를</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南姑</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">스리랑</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南姑</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">돌</t>
         </is>
       </c>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="P6" s="14"/>
+      <c r="Q6" s="16"/>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="14"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="18"/>
+      <c r="N7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="O7" s="18"/>
+      <c r="P7" s="14"/>
+      <c r="Q7" s="18"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢南</t>
         </is>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" s="20"/>
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">무리</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">꽂아</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="I8" s="20"/>
+      <c r="J8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="K8" s="20"/>
+      <c r="L8" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 姑</t>
-        </is>
-      </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="M8" s="20"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="20"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="20"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑南</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">성생을</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南姑</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">무명</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢南</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢南</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">꽂아나</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">와지직</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南姑</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">잘</t>
         </is>
       </c>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="P9" s="14"/>
+      <c r="Q9" s="16"/>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="14"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢南</t>
         </is>
       </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="M10" s="18"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="18"/>
+      <c r="P10" s="14"/>
+      <c r="Q10" s="18"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑姑</t>
         </is>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" s="20"/>
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">무</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G11" s="20"/>
+      <c r="H11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="I11" s="20"/>
+      <c r="J11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="K11" s="20"/>
+      <c r="L11" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 姑</t>
-        </is>
-      </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="M11" s="20"/>
+      <c r="N11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O11" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">돈다</t>
         </is>
       </c>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="P11" s="14"/>
+      <c r="Q11" s="20"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="E12" s="16"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K12" s="3"/>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="K12" s="17"/>
+      <c r="L12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="M12" s="16"/>
+      <c r="N12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南姑</t>
         </is>
       </c>
-      <c r="O12" s="2"/>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3" t="inlineStr">
+      <c r="O12" s="16"/>
+      <c r="P12" s="15"/>
+      <c r="Q12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">돌아라</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2" t="inlineStr">
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C13" s="18"/>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E13" s="18"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="18"/>
+      <c r="L13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="M13" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="O13" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="2"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="P13" s="14"/>
+      <c r="Q13" s="18"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C14" s="20"/>
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="20"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="14"/>
+      <c r="Q14" s="20"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:Q2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="76"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/물레타령.xlsx
+++ b/sheets/민요/검수/물레타령.xlsx
@@ -413,7 +413,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I13" s="2"/>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I28" s="2"/>
@@ -2138,12 +2138,12 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I43" s="2"/>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I67" s="2"/>
@@ -3546,7 +3546,7 @@
       <c r="I5" s="10"/>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K5" s="10"/>
@@ -3706,7 +3706,7 @@
       <c r="C8" s="10"/>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E8" s="10"/>
@@ -3718,7 +3718,7 @@
       <c r="G8" s="10"/>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I8" s="10"/>
@@ -4093,7 +4093,7 @@
       <c r="M14" s="10"/>
       <c r="N14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O14" s="10"/>

--- a/sheets/민요/검수/물레타령.xlsx
+++ b/sheets/민요/검수/물레타령.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3374,731 +3415,731 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">물레타령</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="B3" s="21"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">위리</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr">
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">대의</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="I3" s="8"/>
-      <c r="J3" s="18" t="inlineStr">
+      <c r="I3" s="22"/>
+      <c r="J3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="K3" s="11" t="inlineStr">
+      <c r="K3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">해당</t>
         </is>
       </c>
-      <c r="L3" s="18" t="inlineStr">
+      <c r="L3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="M3" s="11" t="inlineStr">
+      <c r="M3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">위리</t>
         </is>
       </c>
-      <c r="N3" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O3" s="11" t="inlineStr">
+      <c r="N3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">물레</t>
         </is>
       </c>
-      <c r="P3" s="17"/>
-      <c r="Q3" s="8"/>
+      <c r="P3" s="21"/>
+      <c r="Q3" s="22"/>
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="B4" s="21"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">명</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G4" s="25"/>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I4" s="25"/>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="L4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M4" s="9" t="inlineStr">
+      <c r="L4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="N4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O4" s="9" t="inlineStr">
+      <c r="N4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="9"/>
+      <c r="P4" s="21"/>
+      <c r="Q4" s="25"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="B5" s="21"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="E5" s="26"/>
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="G5" s="26"/>
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="I5" s="26"/>
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K5" s="10"/>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="K5" s="26"/>
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M5" s="10"/>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="M5" s="26"/>
+      <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O5" s="10"/>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="10"/>
+      <c r="O5" s="26"/>
+      <c r="P5" s="21"/>
+      <c r="Q5" s="26"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="B6" s="21"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">실도</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">위에</t>
         </is>
       </c>
-      <c r="H6" s="18" t="inlineStr">
+      <c r="H6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="I6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">하송</t>
         </is>
       </c>
-      <c r="J6" s="18" t="inlineStr">
+      <c r="J6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
+      <c r="K6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">와지</t>
         </is>
       </c>
-      <c r="L6" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M6" s="11" t="inlineStr">
+      <c r="L6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">스리</t>
         </is>
       </c>
-      <c r="N6" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O6" s="11" t="inlineStr">
+      <c r="N6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">물레</t>
         </is>
       </c>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="8"/>
+      <c r="P6" s="21"/>
+      <c r="Q6" s="22"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="B7" s="21"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潕</t>
         </is>
       </c>
-      <c r="G7" s="12"/>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="G7" s="27"/>
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="I7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">이를</t>
         </is>
       </c>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="K7" s="9" t="inlineStr">
+      <c r="K7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">직직</t>
         </is>
       </c>
-      <c r="L7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="L7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="N7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O7" s="9" t="inlineStr">
+      <c r="N7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="P7" s="17"/>
-      <c r="Q7" s="9"/>
+      <c r="P7" s="21"/>
+      <c r="Q7" s="25"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="B8" s="21"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="E8" s="26"/>
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="G8" s="26"/>
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I8" s="10"/>
-      <c r="J8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="I8" s="26"/>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K8" s="26"/>
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M8" s="10"/>
-      <c r="N8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O8" s="10"/>
-      <c r="P8" s="17"/>
-      <c r="Q8" s="10"/>
+      <c r="M8" s="26"/>
+      <c r="N8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O8" s="26"/>
+      <c r="P8" s="21"/>
+      <c r="Q8" s="26"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="B9" s="21"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">우리</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 潢</t>
         </is>
       </c>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="G9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">무명</t>
         </is>
       </c>
-      <c r="H9" s="18" t="inlineStr">
+      <c r="H9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 潢</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr">
+      <c r="I9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃아</t>
         </is>
       </c>
-      <c r="J9" s="18" t="inlineStr">
+      <c r="J9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 潢</t>
         </is>
       </c>
-      <c r="K9" s="11" t="inlineStr">
+      <c r="K9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">와지</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M9" s="8" t="inlineStr">
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">잘</t>
         </is>
       </c>
-      <c r="N9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O9" s="8" t="inlineStr">
+      <c r="N9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">병</t>
         </is>
       </c>
-      <c r="P9" s="17"/>
-      <c r="Q9" s="8"/>
+      <c r="P9" s="21"/>
+      <c r="Q9" s="22"/>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="B10" s="21"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E10" s="12"/>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="E10" s="27"/>
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="G10" s="25"/>
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="I10" s="9" t="inlineStr">
+      <c r="I10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">바</t>
         </is>
       </c>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="K10" s="9" t="inlineStr">
+      <c r="K10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">직직</t>
         </is>
       </c>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M10" s="9"/>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="M10" s="25"/>
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O10" s="9" t="inlineStr">
+      <c r="O10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">병</t>
         </is>
       </c>
-      <c r="P10" s="17"/>
-      <c r="Q10" s="9"/>
+      <c r="P10" s="21"/>
+      <c r="Q10" s="25"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="B11" s="21"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="E11" s="26"/>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G11" s="26"/>
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="I11" s="26"/>
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M11" s="10"/>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="K11" s="26"/>
+      <c r="L11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M11" s="26"/>
+      <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O11" s="10" t="inlineStr">
+      <c r="O11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">빙</t>
         </is>
       </c>
-      <c r="P11" s="17"/>
-      <c r="Q11" s="10"/>
+      <c r="P11" s="21"/>
+      <c r="Q11" s="26"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">즉</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">죽</t>
         </is>
       </c>
-      <c r="J12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">껵</t>
         </is>
       </c>
-      <c r="L12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">돈</t>
         </is>
       </c>
-      <c r="N12" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O12" s="11" t="inlineStr">
+      <c r="N12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">돌아</t>
         </is>
       </c>
-      <c r="P12" s="17"/>
-      <c r="Q12" s="8"/>
+      <c r="P12" s="21"/>
+      <c r="Q12" s="22"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="B13" s="21"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E13" s="25"/>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
       </c>
-      <c r="J13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="L13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M13" s="9" t="inlineStr">
+      <c r="L13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="N13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O13" s="9" t="inlineStr">
+      <c r="N13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="P13" s="17"/>
-      <c r="Q13" s="9"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="25"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="B14" s="21"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="E14" s="28"/>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="G14" s="26"/>
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="I14" s="26"/>
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="K14" s="26"/>
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="17" t="inlineStr">
+      <c r="M14" s="26"/>
+      <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O14" s="10"/>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="10"/>
+      <c r="O14" s="26"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/물레타령.xlsx
+++ b/sheets/민요/검수/물레타령.xlsx
@@ -3392,28 +3392,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21"/>
       <c r="C3" s="22"/>
@@ -3504,7 +3504,7 @@
       <c r="P3" s="21"/>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="25"/>
@@ -3563,7 +3563,7 @@
       <c r="P4" s="21"/>
       <c r="Q4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="26"/>
@@ -3606,7 +3606,7 @@
       <c r="P5" s="21"/>
       <c r="Q5" s="26"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="22"/>
@@ -3676,7 +3676,7 @@
       <c r="P6" s="21"/>
       <c r="Q6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="25"/>
@@ -3741,7 +3741,7 @@
       <c r="P7" s="21"/>
       <c r="Q7" s="25"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="26"/>
@@ -3784,7 +3784,7 @@
       <c r="P8" s="21"/>
       <c r="Q8" s="26"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
@@ -3854,7 +3854,7 @@
       <c r="P9" s="21"/>
       <c r="Q9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="25"/>
@@ -3911,7 +3911,7 @@
       <c r="P10" s="21"/>
       <c r="Q10" s="25"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="26"/>
@@ -3960,7 +3960,7 @@
       <c r="P11" s="21"/>
       <c r="Q11" s="26"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
       <c r="P12" s="21"/>
       <c r="Q12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="25"/>
@@ -4098,19 +4098,19 @@
       <c r="P13" s="21"/>
       <c r="Q13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="26"/>
       <c r="D14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E14" s="28"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G14" s="26"/>
@@ -4122,13 +4122,13 @@
       <c r="I14" s="26"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K14" s="26"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M14" s="26"/>

--- a/sheets/민요/검수/물레타령.xlsx
+++ b/sheets/민요/검수/물레타령.xlsx
@@ -3448,7 +3448,8 @@
       </c>
       <c r="E3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">위리</t>
+          <t xml:space="preserve">위
+리</t>
         </is>
       </c>
       <c r="F3" s="23" t="inlineStr">
@@ -3459,7 +3460,8 @@
       </c>
       <c r="G3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">대의</t>
+          <t xml:space="preserve">대
+의</t>
         </is>
       </c>
       <c r="H3" s="21" t="inlineStr">
@@ -3477,7 +3479,8 @@
       </c>
       <c r="K3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">해당</t>
+          <t xml:space="preserve">해
+당</t>
         </is>
       </c>
       <c r="L3" s="23" t="inlineStr">
@@ -3488,7 +3491,8 @@
       </c>
       <c r="M3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">위리</t>
+          <t xml:space="preserve">위
+리</t>
         </is>
       </c>
       <c r="N3" s="23" t="inlineStr">
@@ -3498,7 +3502,8 @@
       </c>
       <c r="O3" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">물레</t>
+          <t xml:space="preserve">물
+레</t>
         </is>
       </c>
       <c r="P3" s="21"/>
@@ -3618,7 +3623,8 @@
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">실도</t>
+          <t xml:space="preserve">실
+도</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr">
@@ -3628,7 +3634,8 @@
       </c>
       <c r="G6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">위에</t>
+          <t xml:space="preserve">위
+에</t>
         </is>
       </c>
       <c r="H6" s="23" t="inlineStr">
@@ -3639,7 +3646,8 @@
       </c>
       <c r="I6" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">하송</t>
+          <t xml:space="preserve">하
+송</t>
         </is>
       </c>
       <c r="J6" s="23" t="inlineStr">
@@ -3650,7 +3658,8 @@
       </c>
       <c r="K6" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">와지</t>
+          <t xml:space="preserve">와
+지</t>
         </is>
       </c>
       <c r="L6" s="23" t="inlineStr">
@@ -3660,7 +3669,8 @@
       </c>
       <c r="M6" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">스리</t>
+          <t xml:space="preserve">스
+리</t>
         </is>
       </c>
       <c r="N6" s="23" t="inlineStr">
@@ -3670,7 +3680,8 @@
       </c>
       <c r="O6" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">물레</t>
+          <t xml:space="preserve">물
+레</t>
         </is>
       </c>
       <c r="P6" s="21"/>
@@ -3704,7 +3715,8 @@
       </c>
       <c r="I7" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">이를</t>
+          <t xml:space="preserve">이
+를</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr">
@@ -3715,7 +3727,8 @@
       </c>
       <c r="K7" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">직직</t>
+          <t xml:space="preserve">직
+직</t>
         </is>
       </c>
       <c r="L7" s="21" t="inlineStr">
@@ -3795,7 +3808,8 @@
       </c>
       <c r="E9" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">우리</t>
+          <t xml:space="preserve">우
+리</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
@@ -3806,7 +3820,8 @@
       </c>
       <c r="G9" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">무명</t>
+          <t xml:space="preserve">무
+명</t>
         </is>
       </c>
       <c r="H9" s="23" t="inlineStr">
@@ -3817,7 +3832,8 @@
       </c>
       <c r="I9" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">꽃아</t>
+          <t xml:space="preserve">꽃
+아</t>
         </is>
       </c>
       <c r="J9" s="23" t="inlineStr">
@@ -3828,7 +3844,8 @@
       </c>
       <c r="K9" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">와지</t>
+          <t xml:space="preserve">와
+지</t>
         </is>
       </c>
       <c r="L9" s="21" t="inlineStr">
@@ -3889,7 +3906,8 @@
       </c>
       <c r="K10" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">직직</t>
+          <t xml:space="preserve">직
+직</t>
         </is>
       </c>
       <c r="L10" s="21" t="inlineStr">
@@ -4029,7 +4047,8 @@
       </c>
       <c r="O12" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">돌아</t>
+          <t xml:space="preserve">돌
+아</t>
         </is>
       </c>
       <c r="P12" s="21"/>

--- a/sheets/민요/검수/물레타령.xlsx
+++ b/sheets/민요/검수/물레타령.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -236,6 +241,24 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3439,14 +3462,14 @@
     <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21"/>
-      <c r="C3" s="22"/>
+      <c r="C3" s="29"/>
       <c r="D3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="E3" s="24" t="inlineStr">
+      <c r="E3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">위
 리</t>
@@ -3458,7 +3481,7 @@
 姑</t>
         </is>
       </c>
-      <c r="G3" s="24" t="inlineStr">
+      <c r="G3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">대
 의</t>
@@ -3470,14 +3493,14 @@
 姑</t>
         </is>
       </c>
-      <c r="I3" s="22"/>
+      <c r="I3" s="29"/>
       <c r="J3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="K3" s="24" t="inlineStr">
+      <c r="K3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">해
 당</t>
@@ -3489,7 +3512,7 @@
 姑</t>
         </is>
       </c>
-      <c r="M3" s="24" t="inlineStr">
+      <c r="M3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">위
 리</t>
@@ -3500,25 +3523,25 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O3" s="24" t="inlineStr">
+      <c r="O3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">물
 레</t>
         </is>
       </c>
       <c r="P3" s="21"/>
-      <c r="Q3" s="22"/>
+      <c r="Q3" s="29"/>
     </row>
     <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
-      <c r="C4" s="25"/>
+      <c r="C4" s="31"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">명</t>
         </is>
@@ -3528,19 +3551,19 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G4" s="25"/>
+      <c r="G4" s="31"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I4" s="25"/>
+      <c r="I4" s="31"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K4" s="25" t="inlineStr">
+      <c r="K4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
@@ -3550,7 +3573,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M4" s="25" t="inlineStr">
+      <c r="M4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
@@ -3560,68 +3583,68 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O4" s="25" t="inlineStr">
+      <c r="O4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
       <c r="P4" s="21"/>
-      <c r="Q4" s="25"/>
+      <c r="Q4" s="31"/>
     </row>
     <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
-      <c r="C5" s="26"/>
+      <c r="C5" s="32"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E5" s="26"/>
+      <c r="E5" s="32"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G5" s="26"/>
+      <c r="G5" s="32"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I5" s="26"/>
+      <c r="I5" s="32"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K5" s="26"/>
+      <c r="K5" s="32"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M5" s="26"/>
+      <c r="M5" s="32"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="O5" s="26"/>
+      <c r="O5" s="32"/>
       <c r="P5" s="21"/>
-      <c r="Q5" s="26"/>
+      <c r="Q5" s="32"/>
     </row>
     <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
-      <c r="C6" s="22"/>
+      <c r="C6" s="29"/>
       <c r="D6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="E6" s="24" t="inlineStr">
+      <c r="E6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">실
 도</t>
@@ -3632,7 +3655,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="G6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">위
 에</t>
@@ -3644,7 +3667,7 @@
 姑</t>
         </is>
       </c>
-      <c r="I6" s="24" t="inlineStr">
+      <c r="I6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">하
 송</t>
@@ -3656,7 +3679,7 @@
 姑</t>
         </is>
       </c>
-      <c r="K6" s="24" t="inlineStr">
+      <c r="K6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">와
 지</t>
@@ -3667,7 +3690,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M6" s="24" t="inlineStr">
+      <c r="M6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">스
 리</t>
@@ -3678,25 +3701,25 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O6" s="24" t="inlineStr">
+      <c r="O6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">물
 레</t>
         </is>
       </c>
       <c r="P6" s="21"/>
-      <c r="Q6" s="22"/>
+      <c r="Q6" s="29"/>
     </row>
     <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
-      <c r="C7" s="25"/>
+      <c r="C7" s="31"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
@@ -3706,14 +3729,14 @@
           <t xml:space="preserve">潕</t>
         </is>
       </c>
-      <c r="G7" s="27"/>
+      <c r="G7" s="33"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="I7" s="25" t="inlineStr">
+      <c r="I7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">이
 를</t>
@@ -3725,7 +3748,7 @@
 姑</t>
         </is>
       </c>
-      <c r="K7" s="25" t="inlineStr">
+      <c r="K7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">직
 직</t>
@@ -3736,7 +3759,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M7" s="25" t="inlineStr">
+      <c r="M7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
@@ -3746,67 +3769,67 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O7" s="25" t="inlineStr">
+      <c r="O7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
       <c r="P7" s="21"/>
-      <c r="Q7" s="25"/>
+      <c r="Q7" s="31"/>
     </row>
     <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
-      <c r="C8" s="26"/>
+      <c r="C8" s="32"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E8" s="26"/>
+      <c r="E8" s="32"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G8" s="26"/>
+      <c r="G8" s="32"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I8" s="26"/>
+      <c r="I8" s="32"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K8" s="26"/>
+      <c r="K8" s="32"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M8" s="26"/>
+      <c r="M8" s="32"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O8" s="26"/>
+      <c r="O8" s="32"/>
       <c r="P8" s="21"/>
-      <c r="Q8" s="26"/>
+      <c r="Q8" s="32"/>
     </row>
     <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
-      <c r="C9" s="22"/>
+      <c r="C9" s="29"/>
       <c r="D9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="E9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">우
 리</t>
@@ -3818,7 +3841,7 @@
 潢</t>
         </is>
       </c>
-      <c r="G9" s="24" t="inlineStr">
+      <c r="G9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">무
 명</t>
@@ -3830,7 +3853,7 @@
 潢</t>
         </is>
       </c>
-      <c r="I9" s="24" t="inlineStr">
+      <c r="I9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃
 아</t>
@@ -3842,7 +3865,7 @@
 潢</t>
         </is>
       </c>
-      <c r="K9" s="24" t="inlineStr">
+      <c r="K9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">와
 지</t>
@@ -3853,7 +3876,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M9" s="22" t="inlineStr">
+      <c r="M9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">잘</t>
         </is>
@@ -3863,37 +3886,37 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O9" s="22" t="inlineStr">
+      <c r="O9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">병</t>
         </is>
       </c>
       <c r="P9" s="21"/>
-      <c r="Q9" s="22"/>
+      <c r="Q9" s="29"/>
     </row>
     <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
-      <c r="C10" s="25"/>
+      <c r="C10" s="31"/>
       <c r="D10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E10" s="27"/>
+      <c r="E10" s="33"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G10" s="25"/>
+      <c r="G10" s="31"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 姑</t>
         </is>
       </c>
-      <c r="I10" s="25" t="inlineStr">
+      <c r="I10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">바</t>
         </is>
@@ -3904,7 +3927,7 @@
 姑</t>
         </is>
       </c>
-      <c r="K10" s="25" t="inlineStr">
+      <c r="K10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">직
 직</t>
@@ -3915,68 +3938,68 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M10" s="25"/>
+      <c r="M10" s="31"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O10" s="25" t="inlineStr">
+      <c r="O10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">병</t>
         </is>
       </c>
       <c r="P10" s="21"/>
-      <c r="Q10" s="25"/>
+      <c r="Q10" s="31"/>
     </row>
     <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
-      <c r="C11" s="26"/>
+      <c r="C11" s="32"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="E11" s="26"/>
+      <c r="E11" s="32"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G11" s="26"/>
+      <c r="G11" s="32"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I11" s="26"/>
+      <c r="I11" s="32"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K11" s="26"/>
+      <c r="K11" s="32"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M11" s="26"/>
+      <c r="M11" s="32"/>
       <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O11" s="26" t="inlineStr">
+      <c r="O11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">빙</t>
         </is>
       </c>
       <c r="P11" s="21"/>
-      <c r="Q11" s="26"/>
+      <c r="Q11" s="32"/>
     </row>
     <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
@@ -3985,7 +4008,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
@@ -3995,7 +4018,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -4005,7 +4028,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">즉</t>
         </is>
@@ -4015,7 +4038,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="I12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">죽</t>
         </is>
@@ -4025,7 +4048,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K12" s="22" t="inlineStr">
+      <c r="K12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">껵</t>
         </is>
@@ -4035,7 +4058,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M12" s="22" t="inlineStr">
+      <c r="M12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">돈</t>
         </is>
@@ -4045,31 +4068,31 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O12" s="24" t="inlineStr">
+      <c r="O12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">돌
 아</t>
         </is>
       </c>
       <c r="P12" s="21"/>
-      <c r="Q12" s="22"/>
+      <c r="Q12" s="29"/>
     </row>
     <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
-      <c r="C13" s="25"/>
+      <c r="C13" s="31"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E13" s="25"/>
+      <c r="E13" s="31"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G13" s="25" t="inlineStr">
+      <c r="G13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
@@ -4079,7 +4102,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I13" s="25" t="inlineStr">
+      <c r="I13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
@@ -4089,7 +4112,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K13" s="25" t="inlineStr">
+      <c r="K13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -4099,7 +4122,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M13" s="25" t="inlineStr">
+      <c r="M13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -4109,56 +4132,56 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O13" s="25" t="inlineStr">
+      <c r="O13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
       <c r="P13" s="21"/>
-      <c r="Q13" s="25"/>
+      <c r="Q13" s="31"/>
     </row>
     <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
-      <c r="C14" s="26"/>
+      <c r="C14" s="32"/>
       <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E14" s="28"/>
+      <c r="E14" s="34"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G14" s="26"/>
+      <c r="G14" s="32"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I14" s="26"/>
+      <c r="I14" s="32"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K14" s="26"/>
+      <c r="K14" s="32"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M14" s="26"/>
+      <c r="M14" s="32"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O14" s="26"/>
+      <c r="O14" s="32"/>
       <c r="P14" s="21"/>
-      <c r="Q14" s="26"/>
+      <c r="Q14" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/물레타령.xlsx
+++ b/sheets/민요/검수/물레타령.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -229,34 +224,16 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -353,7 +330,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">73</t>
+          <t xml:space="preserve">69</t>
         </is>
       </c>
     </row>
@@ -365,7 +342,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
     </row>
@@ -401,7 +378,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">비고 25%</t>
+          <t xml:space="preserve">비고 22%</t>
         </is>
       </c>
     </row>
@@ -429,7 +406,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">인쇄 양식, 줄 번호 1~8(오른쪽부터), 정간 1~12. 12정간·굵은 선 3칸마다 → 중모리 3/4. 오른쪽 여백 "남도민요 물레타령 중모리". 상단에 2절(7·6줄)·1절(5·4줄)·후렴(3·2줄) 묶음 표기. 하단 ※ 요성/꾸밈 기호 범례(潢 등)는 본문 밖이라 생략. 1·8줄은 빈 칸. 율명 옆 물결/꾸밈선은 생략. AI 재판독 초안.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 12정간 양식(굵은 선 3칸마다) → 중모리 3/4·12. 인쇄 줄번호 1·8은 빈 줄이라 제외, 인쇄 2~7 = 줄1~6. 위쪽 묶음: 후렴=인쇄3·2(줄2·1), 1절=5·4(줄4·3), 2절=7·6(줄6·5). 오른쪽 여백 "남도민요 물레타령 중모리". 율명 오른쪽 겹꺾쇠 꾸밈은 ^ 로 적음(하단 범례 ※潢^→潢無 는 본문 밖이라 생략). 괄호 친 (無)는 無 로 적고 비고. 한 곡.</t>
         </is>
       </c>
     </row>
@@ -604,10 +581,10 @@
         </is>
       </c>
       <c r="C2" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2">
         <v>1</v>
@@ -615,26 +592,23 @@
       <c r="F2" s="2">
         <v>1</v>
       </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑|姑</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+姑</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">물레</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">물레야</t>
-        </is>
-      </c>
+      <c r="J2" s="4"/>
       <c r="K2" s="2"/>
     </row>
     <row r="3">
@@ -647,10 +621,10 @@
         </is>
       </c>
       <c r="C3" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2">
         <v>2</v>
@@ -686,10 +660,10 @@
         </is>
       </c>
       <c r="C4" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" s="2">
         <v>3</v>
@@ -697,18 +671,22 @@
       <c r="F4" s="2">
         <v>1</v>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="4"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黃^</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黃^</t>
+        </is>
+      </c>
+      <c r="I4" s="3"/>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">氵 없음(黃), 潢?</t>
+        </is>
+      </c>
       <c r="K4" s="2"/>
     </row>
     <row r="5">
@@ -721,10 +699,10 @@
         </is>
       </c>
       <c r="C5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" s="2">
         <v>4</v>
@@ -732,26 +710,23 @@
       <c r="F5" s="2">
         <v>2</v>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑|姑</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+姑</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">물레</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">물레야</t>
-        </is>
-      </c>
+      <c r="J5" s="4"/>
       <c r="K5" s="2"/>
     </row>
     <row r="6">
@@ -764,10 +739,10 @@
         </is>
       </c>
       <c r="C6" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="2">
         <v>5</v>
@@ -803,10 +778,10 @@
         </is>
       </c>
       <c r="C7" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2">
         <v>6</v>
@@ -816,12 +791,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I7" s="2"/>
@@ -838,10 +813,10 @@
         </is>
       </c>
       <c r="C8" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" s="2">
         <v>7</v>
@@ -851,17 +826,17 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">병</t>
+          <t xml:space="preserve">빙</t>
         </is>
       </c>
       <c r="J8" s="4"/>
@@ -877,10 +852,10 @@
         </is>
       </c>
       <c r="C9" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" s="2">
         <v>8</v>
@@ -888,22 +863,26 @@
       <c r="F9" s="2">
         <v>3</v>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">병</t>
-        </is>
-      </c>
-      <c r="J9" s="4"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">빙</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아래 물결선(생략)</t>
+        </is>
+      </c>
       <c r="K9" s="2"/>
     </row>
     <row r="10">
@@ -916,10 +895,10 @@
         </is>
       </c>
       <c r="C10" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" s="2">
         <v>9</v>
@@ -929,12 +908,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -955,10 +934,10 @@
         </is>
       </c>
       <c r="C11" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" s="2">
         <v>10</v>
@@ -966,26 +945,23 @@
       <c r="F11" s="2">
         <v>4</v>
       </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南|南</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+南</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">돌아</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">돌아라</t>
-        </is>
-      </c>
+      <c r="J11" s="4"/>
       <c r="K11" s="2"/>
     </row>
     <row r="12">
@@ -998,10 +974,10 @@
         </is>
       </c>
       <c r="C12" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" s="2">
         <v>11</v>
@@ -1037,10 +1013,10 @@
         </is>
       </c>
       <c r="C13" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" s="2">
         <v>12</v>
@@ -1072,10 +1048,10 @@
         </is>
       </c>
       <c r="C14" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14" s="2">
         <v>1</v>
@@ -1085,23 +1061,23 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|姑</t>
+          <t xml:space="preserve">南|南</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-姑</t>
+南</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">위리</t>
+          <t xml:space="preserve">워리</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">위리랑</t>
+          <t xml:space="preserve">가사 워/위?</t>
         </is>
       </c>
       <c r="K14" s="2"/>
@@ -1116,10 +1092,10 @@
         </is>
       </c>
       <c r="C15" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" s="2">
         <v>2</v>
@@ -1129,17 +1105,17 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">랑</t>
+          <t xml:space="preserve">렁</t>
         </is>
       </c>
       <c r="J15" s="4"/>
@@ -1155,10 +1131,10 @@
         </is>
       </c>
       <c r="C16" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" s="2">
         <v>3</v>
@@ -1168,12 +1144,13 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–|姑</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–
+姑</t>
         </is>
       </c>
       <c r="I16" s="2"/>
@@ -1190,10 +1167,10 @@
         </is>
       </c>
       <c r="C17" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17" s="2">
         <v>4</v>
@@ -1201,26 +1178,23 @@
       <c r="F17" s="2">
         <v>2</v>
       </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑|–南</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+–南</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">스리</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">스리랑</t>
-        </is>
-      </c>
+      <c r="J17" s="4"/>
       <c r="K17" s="2"/>
     </row>
     <row r="18">
@@ -1233,10 +1207,10 @@
         </is>
       </c>
       <c r="C18" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" s="2">
         <v>5</v>
@@ -1246,17 +1220,17 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">랑</t>
+          <t xml:space="preserve">렁</t>
         </is>
       </c>
       <c r="J18" s="4"/>
@@ -1272,10 +1246,10 @@
         </is>
       </c>
       <c r="C19" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19" s="2">
         <v>6</v>
@@ -1285,12 +1259,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I19" s="2"/>
@@ -1307,10 +1281,10 @@
         </is>
       </c>
       <c r="C20" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" s="2">
         <v>7</v>
@@ -1320,12 +1294,13 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南|–㴌</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南
+–㴌</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1346,10 +1321,10 @@
         </is>
       </c>
       <c r="C21" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D21" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E21" s="2">
         <v>8</v>
@@ -1359,15 +1334,19 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I21" s="2"/>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도</t>
+        </is>
+      </c>
       <c r="J21" s="4"/>
       <c r="K21" s="2"/>
     </row>
@@ -1381,10 +1360,10 @@
         </is>
       </c>
       <c r="C22" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D22" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22" s="2">
         <v>9</v>
@@ -1394,12 +1373,13 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">–|姑</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">–
+姑</t>
         </is>
       </c>
       <c r="I22" s="2"/>
@@ -1416,10 +1396,10 @@
         </is>
       </c>
       <c r="C23" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D23" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23" s="2">
         <v>10</v>
@@ -1429,12 +1409,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1455,10 +1435,10 @@
         </is>
       </c>
       <c r="C24" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D24" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E24" s="2">
         <v>11</v>
@@ -1468,12 +1448,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1494,10 +1474,10 @@
         </is>
       </c>
       <c r="C25" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D25" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E25" s="2">
         <v>12</v>
@@ -1507,12 +1487,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I25" s="2"/>
@@ -1529,10 +1509,10 @@
         </is>
       </c>
       <c r="C26" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D26" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E26" s="2">
         <v>1</v>
@@ -1540,27 +1520,23 @@
       <c r="F26" s="2">
         <v>1</v>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑|姑</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">해당</t>
         </is>
       </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">해당화</t>
-        </is>
-      </c>
+      <c r="J26" s="4"/>
       <c r="K26" s="2"/>
     </row>
     <row r="27">
@@ -1573,10 +1549,10 @@
         </is>
       </c>
       <c r="C27" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D27" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E27" s="2">
         <v>2</v>
@@ -1612,10 +1588,10 @@
         </is>
       </c>
       <c r="C28" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D28" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E28" s="2">
         <v>3</v>
@@ -1623,18 +1599,22 @@
       <c r="F28" s="2">
         <v>1</v>
       </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I28" s="2"/>
-      <c r="J28" s="4"/>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黃^</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黃^</t>
+        </is>
+      </c>
+      <c r="I28" s="3"/>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">氵 없음(黃), 潢?</t>
+        </is>
+      </c>
       <c r="K28" s="2"/>
     </row>
     <row r="29">
@@ -1647,10 +1627,10 @@
         </is>
       </c>
       <c r="C29" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D29" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E29" s="2">
         <v>4</v>
@@ -1671,12 +1651,12 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">와지</t>
+          <t xml:space="preserve">하송</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">와지직직</t>
+          <t xml:space="preserve">가사 하/한?</t>
         </is>
       </c>
       <c r="K29" s="2"/>
@@ -1691,10 +1671,10 @@
         </is>
       </c>
       <c r="C30" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D30" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E30" s="2">
         <v>5</v>
@@ -1715,7 +1695,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">직직</t>
+          <t xml:space="preserve">이를</t>
         </is>
       </c>
       <c r="J30" s="4"/>
@@ -1731,10 +1711,10 @@
         </is>
       </c>
       <c r="C31" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D31" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E31" s="2">
         <v>6</v>
@@ -1744,12 +1724,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I31" s="2"/>
@@ -1766,10 +1746,10 @@
         </is>
       </c>
       <c r="C32" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D32" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E32" s="2">
         <v>7</v>
@@ -1777,27 +1757,23 @@
       <c r="F32" s="2">
         <v>3</v>
       </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑|潢</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-潢</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南|–潢</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+–潢</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">와지</t>
         </is>
       </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">와지직직</t>
-        </is>
-      </c>
+      <c r="J32" s="4"/>
       <c r="K32" s="2"/>
     </row>
     <row r="33">
@@ -1810,10 +1786,10 @@
         </is>
       </c>
       <c r="C33" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D33" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E33" s="2">
         <v>8</v>
@@ -1823,18 +1799,18 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|姑</t>
+          <t xml:space="preserve">潢|潢</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-姑</t>
+潢</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">직직</t>
+          <t xml:space="preserve">지직</t>
         </is>
       </c>
       <c r="J33" s="4"/>
@@ -1850,10 +1826,10 @@
         </is>
       </c>
       <c r="C34" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D34" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E34" s="2">
         <v>9</v>
@@ -1863,16 +1839,19 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|姑</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-姑</t>
-        </is>
-      </c>
-      <c r="I34" s="2"/>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">끈</t>
+        </is>
+      </c>
       <c r="J34" s="4"/>
       <c r="K34" s="2"/>
     </row>
@@ -1886,10 +1865,10 @@
         </is>
       </c>
       <c r="C35" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D35" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E35" s="2">
         <v>10</v>
@@ -1899,17 +1878,17 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">껵</t>
+          <t xml:space="preserve">꺽</t>
         </is>
       </c>
       <c r="J35" s="4"/>
@@ -1925,10 +1904,10 @@
         </is>
       </c>
       <c r="C36" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D36" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E36" s="2">
         <v>11</v>
@@ -1964,10 +1943,10 @@
         </is>
       </c>
       <c r="C37" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D37" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E37" s="2">
         <v>12</v>
@@ -1977,12 +1956,12 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I37" s="2"/>
@@ -1999,10 +1978,10 @@
         </is>
       </c>
       <c r="C38" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D38" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E38" s="2">
         <v>1</v>
@@ -2012,16 +1991,20 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|姑</t>
+          <t xml:space="preserve">南|南</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-姑</t>
-        </is>
-      </c>
-      <c r="I38" s="2"/>
+          <t xml:space="preserve">南
+南</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우리</t>
+        </is>
+      </c>
       <c r="J38" s="4"/>
       <c r="K38" s="2"/>
     </row>
@@ -2035,10 +2018,10 @@
         </is>
       </c>
       <c r="C39" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D39" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E39" s="2">
         <v>2</v>
@@ -2048,12 +2031,12 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I39" s="2"/>
@@ -2070,10 +2053,10 @@
         </is>
       </c>
       <c r="C40" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D40" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E40" s="2">
         <v>3</v>
@@ -2083,15 +2066,19 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I40" s="2"/>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">님</t>
+        </is>
+      </c>
       <c r="J40" s="4"/>
       <c r="K40" s="2"/>
     </row>
@@ -2105,10 +2092,10 @@
         </is>
       </c>
       <c r="C41" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D41" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E41" s="2">
         <v>4</v>
@@ -2116,27 +2103,23 @@
       <c r="F41" s="2">
         <v>2</v>
       </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑|姑</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑|–南</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-姑</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">하송</t>
-        </is>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">하송이를</t>
-        </is>
-      </c>
+–南</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">머리</t>
+        </is>
+      </c>
+      <c r="J41" s="4"/>
       <c r="K41" s="2"/>
     </row>
     <row r="42">
@@ -2149,10 +2132,10 @@
         </is>
       </c>
       <c r="C42" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D42" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E42" s="2">
         <v>5</v>
@@ -2160,23 +2143,27 @@
       <c r="F42" s="2">
         <v>2</v>
       </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑|姑</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-姑</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이를</t>
-        </is>
-      </c>
-      <c r="J42" s="4"/>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^|無</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^
+無</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">위에</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無 괄호 (無)</t>
+        </is>
+      </c>
       <c r="K42" s="2"/>
     </row>
     <row r="43">
@@ -2189,10 +2176,10 @@
         </is>
       </c>
       <c r="C43" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D43" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E43" s="2">
         <v>6</v>
@@ -2202,15 +2189,19 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I43" s="2"/>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
       <c r="J43" s="4"/>
       <c r="K43" s="2"/>
     </row>
@@ -2224,10 +2215,10 @@
         </is>
       </c>
       <c r="C44" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D44" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E44" s="2">
         <v>7</v>
@@ -2237,23 +2228,23 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|潢</t>
+          <t xml:space="preserve">南|–潢</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-潢</t>
+          <t xml:space="preserve">南
+–潢</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">꽃아</t>
+          <t xml:space="preserve">꽂아</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">꽃아바</t>
+          <t xml:space="preserve">潢 왼쪽 위 작은 c 표시</t>
         </is>
       </c>
       <c r="K44" s="2"/>
@@ -2268,10 +2259,10 @@
         </is>
       </c>
       <c r="C45" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D45" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E45" s="2">
         <v>8</v>
@@ -2279,23 +2270,27 @@
       <c r="F45" s="2">
         <v>3</v>
       </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢|姑</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-姑</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바</t>
-        </is>
-      </c>
-      <c r="J45" s="4"/>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^|–南</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^
+–南</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">마</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢 위 덧쓴 c 표시</t>
+        </is>
+      </c>
       <c r="K45" s="2"/>
     </row>
     <row r="46">
@@ -2308,10 +2303,10 @@
         </is>
       </c>
       <c r="C46" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D46" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E46" s="2">
         <v>9</v>
@@ -2321,15 +2316,19 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I46" s="2"/>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나</t>
+        </is>
+      </c>
       <c r="J46" s="4"/>
       <c r="K46" s="2"/>
     </row>
@@ -2343,10 +2342,10 @@
         </is>
       </c>
       <c r="C47" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D47" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E47" s="2">
         <v>10</v>
@@ -2354,22 +2353,26 @@
       <c r="F47" s="2">
         <v>4</v>
       </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">죽</t>
         </is>
       </c>
-      <c r="J47" s="4"/>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 죽/주?</t>
+        </is>
+      </c>
       <c r="K47" s="2"/>
     </row>
     <row r="48">
@@ -2382,10 +2385,10 @@
         </is>
       </c>
       <c r="C48" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D48" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E48" s="2">
         <v>11</v>
@@ -2395,12 +2398,12 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -2421,10 +2424,10 @@
         </is>
       </c>
       <c r="C49" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D49" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E49" s="2">
         <v>12</v>
@@ -2434,12 +2437,12 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="I49" s="2"/>
@@ -2456,10 +2459,10 @@
         </is>
       </c>
       <c r="C50" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D50" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E50" s="2">
         <v>1</v>
@@ -2467,27 +2470,23 @@
       <c r="F50" s="2">
         <v>1</v>
       </c>
-      <c r="G50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南|姑</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-姑</t>
-        </is>
-      </c>
-      <c r="I50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대의</t>
-        </is>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대의위에</t>
-        </is>
-      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢|潢</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+潢</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">무명</t>
+        </is>
+      </c>
+      <c r="J50" s="4"/>
       <c r="K50" s="2"/>
     </row>
     <row r="51">
@@ -2500,25 +2499,25 @@
         </is>
       </c>
       <c r="C51" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D51" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E51" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F51" s="2">
         <v>1</v>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="I51" s="2"/>
@@ -2535,28 +2534,33 @@
         </is>
       </c>
       <c r="C52" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D52" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E52" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F52" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">南|潢^</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I52" s="2"/>
+          <t xml:space="preserve">南
+潢^</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">실</t>
+        </is>
+      </c>
       <c r="J52" s="4"/>
       <c r="K52" s="2"/>
     </row>
@@ -2570,30 +2574,30 @@
         </is>
       </c>
       <c r="C53" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D53" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E53" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F53" s="2">
         <v>2</v>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">위에</t>
+          <t xml:space="preserve">도</t>
         </is>
       </c>
       <c r="J53" s="4"/>
@@ -2609,33 +2613,30 @@
         </is>
       </c>
       <c r="C54" s="2">
+        <v>5</v>
+      </c>
+      <c r="D54" s="2">
+        <v>5</v>
+      </c>
+      <c r="E54" s="2">
         <v>6</v>
       </c>
-      <c r="D54" s="2">
-        <v>6</v>
-      </c>
-      <c r="E54" s="2">
-        <v>5</v>
-      </c>
       <c r="F54" s="2">
         <v>2</v>
       </c>
-      <c r="G54" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="I54" s="3"/>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕 흐림, 확실치 않음</t>
-        </is>
-      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|△</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I54" s="2"/>
+      <c r="J54" s="4"/>
       <c r="K54" s="2"/>
     </row>
     <row r="55">
@@ -2648,28 +2649,32 @@
         </is>
       </c>
       <c r="C55" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D55" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E55" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F55" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I55" s="2"/>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">뒷</t>
+        </is>
+      </c>
       <c r="J55" s="4"/>
       <c r="K55" s="2"/>
     </row>
@@ -2683,36 +2688,31 @@
         </is>
       </c>
       <c r="C56" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D56" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E56" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F56" s="2">
         <v>3</v>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|潢</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-潢</t>
-        </is>
-      </c>
-      <c r="I56" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">무명</t>
-        </is>
-      </c>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I56" s="3"/>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">무명</t>
+          <t xml:space="preserve">괄호 (無), 위 작은 표시</t>
         </is>
       </c>
       <c r="K56" s="2"/>
@@ -2727,29 +2727,38 @@
         </is>
       </c>
       <c r="C57" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D57" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E57" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F57" s="2">
         <v>3</v>
       </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I57" s="2"/>
-      <c r="J57" s="4"/>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑㴌|潢^</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑㴌
+潢^</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">짜기</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">윗줄 두 글자: 왼쪽 氵 불분명(姑?), 오른쪽 㴌 옆 c 표시</t>
+        </is>
+      </c>
       <c r="K57" s="2"/>
     </row>
     <row r="58">
@@ -2762,28 +2771,32 @@
         </is>
       </c>
       <c r="C58" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D58" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E58" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F58" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I58" s="2"/>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">는</t>
+        </is>
+      </c>
       <c r="J58" s="4"/>
       <c r="K58" s="2"/>
     </row>
@@ -2797,32 +2810,28 @@
         </is>
       </c>
       <c r="C59" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D59" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E59" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F59" s="2">
         <v>4</v>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">즉</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I59" s="2"/>
       <c r="J59" s="4"/>
       <c r="K59" s="2"/>
     </row>
@@ -2836,32 +2845,28 @@
         </is>
       </c>
       <c r="C60" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D60" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E60" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F60" s="2">
         <v>4</v>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">△</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">세</t>
-        </is>
-      </c>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="I60" s="2"/>
       <c r="J60" s="4"/>
       <c r="K60" s="2"/>
     </row>
@@ -2881,22 +2886,26 @@
         <v>6</v>
       </c>
       <c r="E61" s="2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F61" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">潢^</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I61" s="2"/>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우리</t>
+        </is>
+      </c>
       <c r="J61" s="4"/>
       <c r="K61" s="2"/>
     </row>
@@ -2910,230 +2919,243 @@
         </is>
       </c>
       <c r="C62" s="2">
+        <v>6</v>
+      </c>
+      <c r="D62" s="2">
+        <v>6</v>
+      </c>
+      <c r="E62" s="2">
+        <v>2</v>
+      </c>
+      <c r="F62" s="2">
+        <v>1</v>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I62" s="3"/>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">괄호 (無), 위 작은 표시</t>
+        </is>
+      </c>
+      <c r="K62" s="2"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2">
+        <v>1</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/물레타령.png</t>
+        </is>
+      </c>
+      <c r="C63" s="2">
+        <v>6</v>
+      </c>
+      <c r="D63" s="2">
+        <v>6</v>
+      </c>
+      <c r="E63" s="2">
+        <v>3</v>
+      </c>
+      <c r="F63" s="2">
+        <v>1</v>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南|潢^</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+潢^</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정</t>
+        </is>
+      </c>
+      <c r="J63" s="4"/>
+      <c r="K63" s="2"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2">
+        <v>1</v>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/물레타령.png</t>
+        </is>
+      </c>
+      <c r="C64" s="2">
+        <v>6</v>
+      </c>
+      <c r="D64" s="2">
+        <v>6</v>
+      </c>
+      <c r="E64" s="2">
+        <v>4</v>
+      </c>
+      <c r="F64" s="2">
+        <v>2</v>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">성</t>
+        </is>
+      </c>
+      <c r="J64" s="4"/>
+      <c r="K64" s="2"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2">
+        <v>1</v>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/물레타령.png</t>
+        </is>
+      </c>
+      <c r="C65" s="2">
+        <v>6</v>
+      </c>
+      <c r="D65" s="2">
+        <v>6</v>
+      </c>
+      <c r="E65" s="2">
+        <v>5</v>
+      </c>
+      <c r="F65" s="2">
+        <v>2</v>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南|潢^</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+潢^</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢 앞 작은 c 표시</t>
+        </is>
+      </c>
+      <c r="K65" s="2"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2">
+        <v>1</v>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/물레타령.png</t>
+        </is>
+      </c>
+      <c r="C66" s="2">
+        <v>6</v>
+      </c>
+      <c r="D66" s="2">
+        <v>6</v>
+      </c>
+      <c r="E66" s="2">
+        <v>6</v>
+      </c>
+      <c r="F66" s="2">
+        <v>2</v>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">을</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢 앞 작은 G 표시</t>
+        </is>
+      </c>
+      <c r="K66" s="2"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2">
+        <v>1</v>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/물레타령.png</t>
+        </is>
+      </c>
+      <c r="C67" s="2">
+        <v>6</v>
+      </c>
+      <c r="D67" s="2">
+        <v>6</v>
+      </c>
+      <c r="E67" s="2">
         <v>7</v>
       </c>
-      <c r="D62" s="2">
-        <v>7</v>
-      </c>
-      <c r="E62" s="2">
-        <v>1</v>
-      </c>
-      <c r="F62" s="2">
-        <v>1</v>
-      </c>
-      <c r="G62" s="3" t="inlineStr">
+      <c r="F67" s="2">
+        <v>3</v>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">南|姑</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
+      <c r="H67" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="I62" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위리</t>
-        </is>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위리명</t>
-        </is>
-      </c>
-      <c r="K62" s="2"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2">
-        <v>1</v>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/물레타령.png</t>
-        </is>
-      </c>
-      <c r="C63" s="2">
-        <v>7</v>
-      </c>
-      <c r="D63" s="2">
-        <v>7</v>
-      </c>
-      <c r="E63" s="2">
-        <v>2</v>
-      </c>
-      <c r="F63" s="2">
-        <v>1</v>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">명</t>
-        </is>
-      </c>
-      <c r="J63" s="4"/>
-      <c r="K63" s="2"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2">
-        <v>1</v>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/물레타령.png</t>
-        </is>
-      </c>
-      <c r="C64" s="2">
-        <v>7</v>
-      </c>
-      <c r="D64" s="2">
-        <v>7</v>
-      </c>
-      <c r="E64" s="2">
-        <v>3</v>
-      </c>
-      <c r="F64" s="2">
-        <v>1</v>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I64" s="2"/>
-      <c r="J64" s="4"/>
-      <c r="K64" s="2"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2">
-        <v>1</v>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/물레타령.png</t>
-        </is>
-      </c>
-      <c r="C65" s="2">
-        <v>7</v>
-      </c>
-      <c r="D65" s="2">
-        <v>7</v>
-      </c>
-      <c r="E65" s="2">
-        <v>4</v>
-      </c>
-      <c r="F65" s="2">
-        <v>2</v>
-      </c>
-      <c r="G65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢|姑</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-姑</t>
-        </is>
-      </c>
-      <c r="I65" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">실도</t>
-        </is>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">실도</t>
-        </is>
-      </c>
-      <c r="K65" s="2"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2">
-        <v>1</v>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/물레타령.png</t>
-        </is>
-      </c>
-      <c r="C66" s="2">
-        <v>7</v>
-      </c>
-      <c r="D66" s="2">
-        <v>7</v>
-      </c>
-      <c r="E66" s="2">
-        <v>5</v>
-      </c>
-      <c r="F66" s="2">
-        <v>2</v>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도</t>
-        </is>
-      </c>
-      <c r="J66" s="4"/>
-      <c r="K66" s="2"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2">
-        <v>1</v>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/물레타령.png</t>
-        </is>
-      </c>
-      <c r="C67" s="2">
-        <v>7</v>
-      </c>
-      <c r="D67" s="2">
-        <v>7</v>
-      </c>
-      <c r="E67" s="2">
-        <v>6</v>
-      </c>
-      <c r="F67" s="2">
-        <v>2</v>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I67" s="2"/>
-      <c r="J67" s="4"/>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">무디</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 무디/우리?</t>
+        </is>
+      </c>
       <c r="K67" s="2"/>
     </row>
     <row r="68">
@@ -3146,37 +3168,33 @@
         </is>
       </c>
       <c r="C68" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D68" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E68" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F68" s="2">
         <v>3</v>
       </c>
-      <c r="G68" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I68" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">우리</t>
-        </is>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">우리</t>
-        </is>
-      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지</t>
+        </is>
+      </c>
+      <c r="J68" s="4"/>
       <c r="K68" s="2"/>
     </row>
     <row r="69">
@@ -3189,33 +3207,29 @@
         </is>
       </c>
       <c r="C69" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D69" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E69" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F69" s="2">
         <v>3</v>
       </c>
-      <c r="G69" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I69" s="3"/>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(無) 괄호 표시</t>
-        </is>
-      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I69" s="2"/>
+      <c r="J69" s="4"/>
       <c r="K69" s="2"/>
     </row>
     <row r="70">
@@ -3228,186 +3242,37 @@
         </is>
       </c>
       <c r="C70" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D70" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E70" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F70" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-姑</t>
-        </is>
-      </c>
-      <c r="I70" s="2"/>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">네</t>
+        </is>
+      </c>
       <c r="J70" s="4"/>
       <c r="K70" s="2"/>
     </row>
-    <row r="71">
-      <c r="A71" s="2">
-        <v>1</v>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/물레타령.png</t>
-        </is>
-      </c>
-      <c r="C71" s="2">
-        <v>7</v>
-      </c>
-      <c r="D71" s="2">
-        <v>7</v>
-      </c>
-      <c r="E71" s="2">
-        <v>10</v>
-      </c>
-      <c r="F71" s="2">
-        <v>4</v>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">는</t>
-        </is>
-      </c>
-      <c r="J71" s="4"/>
-      <c r="K71" s="2"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2">
-        <v>1</v>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/물레타령.png</t>
-        </is>
-      </c>
-      <c r="C72" s="2">
-        <v>7</v>
-      </c>
-      <c r="D72" s="2">
-        <v>7</v>
-      </c>
-      <c r="E72" s="2">
-        <v>11</v>
-      </c>
-      <c r="F72" s="2">
-        <v>4</v>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I72" s="2"/>
-      <c r="J72" s="4"/>
-      <c r="K72" s="2"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2">
-        <v>1</v>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/물레타령.png</t>
-        </is>
-      </c>
-      <c r="C73" s="2">
-        <v>7</v>
-      </c>
-      <c r="D73" s="2">
-        <v>7</v>
-      </c>
-      <c r="E73" s="2">
-        <v>12</v>
-      </c>
-      <c r="F73" s="2">
-        <v>4</v>
-      </c>
-      <c r="G73" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I73" s="3"/>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작은 ∧/점 모양, 확실치 않음</t>
-        </is>
-      </c>
-      <c r="K73" s="2"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2">
-        <v>1</v>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/물레타령.png</t>
-        </is>
-      </c>
-      <c r="C74" s="2">
-        <v>8</v>
-      </c>
-      <c r="D74" s="2">
-        <v>8</v>
-      </c>
-      <c r="E74" s="2">
-        <v>10</v>
-      </c>
-      <c r="F74" s="2">
-        <v>4</v>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">네</t>
-        </is>
-      </c>
-      <c r="J74" s="4"/>
-      <c r="K74" s="2"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K74"/>
+  <autoFilter ref="A1:K70"/>
 </worksheet>
 </file>
 
@@ -3427,16 +3292,12 @@
     <col min="11" max="11" width="6" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="12" customWidth="1"/>
-    <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="12" customWidth="1"/>
-    <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="55.19" customHeight="1">
+    <row r="2" ht="55.96" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3454,741 +3315,712 @@
       <c r="K2" s="20"/>
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
-      <c r="N2" s="20"/>
-      <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
-      <c r="Q2" s="20"/>
-    </row>
-    <row r="3" ht="55.19" customHeight="1">
+    </row>
+    <row r="3" ht="55.96" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="23" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="C3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우
+리</t>
+        </is>
+      </c>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+潢</t>
+        </is>
+      </c>
+      <c r="E3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">무
+명</t>
+        </is>
+      </c>
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+南</t>
+        </is>
+      </c>
+      <c r="G3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우
+리</t>
+        </is>
+      </c>
+      <c r="H3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+姑</t>
+        </is>
+      </c>
+      <c r="I3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해
+당</t>
+        </is>
+      </c>
+      <c r="J3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+南</t>
+        </is>
+      </c>
+      <c r="K3" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">워
+리</t>
+        </is>
+      </c>
+      <c r="L3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+姑</t>
+        </is>
+      </c>
+      <c r="M3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">물
+레</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="55.96" customHeight="1">
+      <c r="A4" s="0"/>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="C4" s="25"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G4" s="26"/>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I4" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">화</t>
+        </is>
+      </c>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K4" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">렁</t>
+        </is>
+      </c>
+      <c r="L4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M4" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">야</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="55.96" customHeight="1">
+      <c r="A5" s="0"/>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+潢^</t>
+        </is>
+      </c>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="E5" s="27"/>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="G5" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">님</t>
+        </is>
+      </c>
+      <c r="H5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黃^</t>
+        </is>
+      </c>
+      <c r="I5" s="28"/>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+姑</t>
+        </is>
+      </c>
+      <c r="K5" s="27"/>
+      <c r="L5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黃^</t>
+        </is>
+      </c>
+      <c r="M5" s="28"/>
+    </row>
+    <row r="6" ht="55.96" customHeight="1">
+      <c r="A6" s="0"/>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">성</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+潢^</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">실</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+–南</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">머
+리</t>
+        </is>
+      </c>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+姑</t>
+        </is>
+      </c>
+      <c r="I6" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하
+송</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+–南</t>
+        </is>
+      </c>
+      <c r="K6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">스
+리</t>
+        </is>
+      </c>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+姑</t>
+        </is>
+      </c>
+      <c r="M6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">물
+레</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="55.96" customHeight="1">
+      <c r="A7" s="0"/>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+潢^</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="E7" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^
+無</t>
+        </is>
+      </c>
+      <c r="G7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">위
+에</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+姑</t>
+        </is>
+      </c>
+      <c r="I7" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이
+를</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="K7" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">렁</t>
+        </is>
+      </c>
+      <c r="L7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M7" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">야</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="55.96" customHeight="1">
+      <c r="A8" s="0"/>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">을</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="E8" s="27"/>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="G8" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I8" s="27"/>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K8" s="27"/>
+      <c r="L8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="M8" s="27"/>
+    </row>
+    <row r="9" ht="55.96" customHeight="1">
+      <c r="A9" s="0"/>
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 姑</t>
         </is>
       </c>
-      <c r="E3" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위
-리</t>
-        </is>
-      </c>
-      <c r="F3" s="23" t="inlineStr">
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">무
+디</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">뒷</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-姑</t>
-        </is>
-      </c>
-      <c r="G3" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대
-의</t>
-        </is>
-      </c>
-      <c r="H3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-姑</t>
-        </is>
-      </c>
-      <c r="I3" s="29"/>
-      <c r="J3" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-姑</t>
-        </is>
-      </c>
-      <c r="K3" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">해
-당</t>
-        </is>
-      </c>
-      <c r="L3" s="23" t="inlineStr">
+–潢</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽂
+아</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-姑</t>
-        </is>
-      </c>
-      <c r="M3" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위
-리</t>
-        </is>
-      </c>
-      <c r="N3" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O3" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">물
-레</t>
-        </is>
-      </c>
-      <c r="P3" s="21"/>
-      <c r="Q3" s="29"/>
-    </row>
-    <row r="4" ht="55.19" customHeight="1">
-      <c r="A4" s="0"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E4" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">명</t>
-        </is>
-      </c>
-      <c r="F4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G4" s="31"/>
-      <c r="H4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I4" s="31"/>
-      <c r="J4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K4" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">화</t>
-        </is>
-      </c>
-      <c r="L4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M4" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">랑</t>
-        </is>
-      </c>
-      <c r="N4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O4" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">야</t>
-        </is>
-      </c>
-      <c r="P4" s="21"/>
-      <c r="Q4" s="31"/>
-    </row>
-    <row r="5" ht="55.19" customHeight="1">
-      <c r="A5" s="0"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="32"/>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E5" s="32"/>
-      <c r="F5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G5" s="32"/>
-      <c r="H5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I5" s="32"/>
-      <c r="J5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K5" s="32"/>
-      <c r="L5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M5" s="32"/>
-      <c r="N5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="O5" s="32"/>
-      <c r="P5" s="21"/>
-      <c r="Q5" s="32"/>
-    </row>
-    <row r="6" ht="55.19" customHeight="1">
-      <c r="A6" s="0"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-姑</t>
-        </is>
-      </c>
-      <c r="E6" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">실
-도</t>
-        </is>
-      </c>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G6" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">위
-에</t>
-        </is>
-      </c>
-      <c r="H6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-姑</t>
-        </is>
-      </c>
-      <c r="I6" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">하
-송</t>
-        </is>
-      </c>
-      <c r="J6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-姑</t>
-        </is>
-      </c>
-      <c r="K6" s="30" t="inlineStr">
+–潢</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">와
 지</t>
         </is>
       </c>
-      <c r="L6" s="23" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+–㴌</t>
+        </is>
+      </c>
+      <c r="K9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">잘</t>
+        </is>
+      </c>
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="M9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">빙</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="55.96" customHeight="1">
+      <c r="A10" s="0"/>
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M6" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">스
-리</t>
-        </is>
-      </c>
-      <c r="N6" s="23" t="inlineStr">
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="E10" s="25"/>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^
+–南</t>
+        </is>
+      </c>
+      <c r="G10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">마</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+潢</t>
+        </is>
+      </c>
+      <c r="I10" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지
+직</t>
+        </is>
+      </c>
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="K10" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도</t>
+        </is>
+      </c>
+      <c r="L10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="M10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">빙</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="55.96" customHeight="1">
+      <c r="A11" s="0"/>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="C11" s="27"/>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑㴌
+潢^</t>
+        </is>
+      </c>
+      <c r="E11" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">짜
+기</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O6" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">물
-레</t>
-        </is>
-      </c>
-      <c r="P6" s="21"/>
-      <c r="Q6" s="29"/>
-    </row>
-    <row r="7" ht="55.19" customHeight="1">
-      <c r="A7" s="0"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도</t>
-        </is>
-      </c>
-      <c r="F7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="G7" s="33"/>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
+      <c r="G11" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="I11" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">끈</t>
+        </is>
+      </c>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
 姑</t>
         </is>
       </c>
-      <c r="I7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이
-를</t>
-        </is>
-      </c>
-      <c r="J7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-姑</t>
-        </is>
-      </c>
-      <c r="K7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">직
-직</t>
-        </is>
-      </c>
-      <c r="L7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">랑</t>
-        </is>
-      </c>
-      <c r="N7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">야</t>
-        </is>
-      </c>
-      <c r="P7" s="21"/>
-      <c r="Q7" s="31"/>
-    </row>
-    <row r="8" ht="55.19" customHeight="1">
-      <c r="A8" s="0"/>
-      <c r="B8" s="21"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="E8" s="32"/>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I8" s="32"/>
-      <c r="J8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K8" s="32"/>
-      <c r="L8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M8" s="32"/>
-      <c r="N8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O8" s="32"/>
-      <c r="P8" s="21"/>
-      <c r="Q8" s="32"/>
-    </row>
-    <row r="9" ht="55.19" customHeight="1">
-      <c r="A9" s="0"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E9" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">우
-리</t>
-        </is>
-      </c>
-      <c r="F9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-潢</t>
-        </is>
-      </c>
-      <c r="G9" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">무
-명</t>
-        </is>
-      </c>
-      <c r="H9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-潢</t>
-        </is>
-      </c>
-      <c r="I9" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">꽃
-아</t>
-        </is>
-      </c>
-      <c r="J9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-潢</t>
-        </is>
-      </c>
-      <c r="K9" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">와
-지</t>
-        </is>
-      </c>
-      <c r="L9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">잘</t>
-        </is>
-      </c>
-      <c r="N9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">병</t>
-        </is>
-      </c>
-      <c r="P9" s="21"/>
-      <c r="Q9" s="29"/>
-    </row>
-    <row r="10" ht="55.19" customHeight="1">
-      <c r="A10" s="0"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="E10" s="33"/>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G10" s="31"/>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-姑</t>
-        </is>
-      </c>
-      <c r="I10" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">바</t>
-        </is>
-      </c>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-姑</t>
-        </is>
-      </c>
-      <c r="K10" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">직
-직</t>
-        </is>
-      </c>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="M10" s="31"/>
-      <c r="N10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="O10" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">병</t>
-        </is>
-      </c>
-      <c r="P10" s="21"/>
-      <c r="Q10" s="31"/>
-    </row>
-    <row r="11" ht="55.19" customHeight="1">
-      <c r="A11" s="0"/>
-      <c r="B11" s="21"/>
-      <c r="C11" s="32"/>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-姑</t>
-        </is>
-      </c>
-      <c r="E11" s="32"/>
-      <c r="F11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G11" s="32"/>
-      <c r="H11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I11" s="32"/>
-      <c r="J11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-姑</t>
-        </is>
-      </c>
-      <c r="K11" s="32"/>
+      <c r="K11" s="27"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M11" s="32"/>
-      <c r="N11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="O11" s="32" t="inlineStr">
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="M11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">빙</t>
         </is>
       </c>
-      <c r="P11" s="21"/>
-      <c r="Q11" s="32"/>
-    </row>
-    <row r="12" ht="55.19" customHeight="1">
+    </row>
+    <row r="12" ht="55.96" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C12" s="29" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E12" s="29" t="inlineStr">
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">즉</t>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">죽</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">죽</t>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꺽</t>
         </is>
       </c>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">껵</t>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">돈</t>
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">돈</t>
-        </is>
-      </c>
-      <c r="N12" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O12" s="30" t="inlineStr">
+          <t xml:space="preserve">南
+南</t>
+        </is>
+      </c>
+      <c r="M12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">돌
 아</t>
         </is>
       </c>
-      <c r="P12" s="21"/>
-      <c r="Q12" s="29"/>
-    </row>
-    <row r="13" ht="55.19" customHeight="1">
+    </row>
+    <row r="13" ht="55.96" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
-      <c r="C13" s="31"/>
+      <c r="C13" s="26"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="E13" s="26"/>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G13" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E13" s="31"/>
-      <c r="F13" s="21" t="inlineStr">
+      <c r="I13" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
+        </is>
+      </c>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K13" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G13" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">세</t>
-        </is>
-      </c>
-      <c r="H13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I13" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">세</t>
-        </is>
-      </c>
-      <c r="J13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K13" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">어</t>
-        </is>
-      </c>
-      <c r="L13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M13" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다</t>
-        </is>
-      </c>
-      <c r="N13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O13" s="31" t="inlineStr">
+      <c r="M13" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="P13" s="21"/>
-      <c r="Q13" s="31"/>
-    </row>
-    <row r="14" ht="55.19" customHeight="1">
+    </row>
+    <row r="14" ht="55.96" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
-      <c r="C14" s="32"/>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="C14" s="27"/>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="E14" s="27"/>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E14" s="34"/>
-      <c r="F14" s="21" t="inlineStr">
+      <c r="G14" s="27"/>
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G14" s="32"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="I14" s="32"/>
+      <c r="I14" s="27"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K14" s="32"/>
+      <c r="K14" s="27"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M14" s="32"/>
-      <c r="N14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="O14" s="32"/>
-      <c r="P14" s="21"/>
-      <c r="Q14" s="32"/>
+      <c r="M14" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B2:Q2"/>
+    <mergeCell ref="B2:M2"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="76"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/물레타령.xlsx
+++ b/sheets/민요/검수/물레타령.xlsx
@@ -607,10 +607,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/물레타령.xlsx
+++ b/sheets/민요/검수/물레타령.xlsx
@@ -553,17 +553,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -680,7 +680,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -738,6 +738,50 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3333,448 +3377,448 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:M14"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="16" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="51.95" customHeight="true">
+      <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+    </row>
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.24" customHeight="true">
+      <c r="B3" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="19" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="9" t="s">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.24" customHeight="true">
+      <c r="B4" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="7" t="s">
+      <c r="C4" s="22"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="G4" s="12"/>
-      <c r="H4" s="7" t="s">
+      <c r="G4" s="23"/>
+      <c r="H4" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="M4" s="12" t="s">
+      <c r="M4" s="23" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.24" customHeight="true">
+      <c r="B5" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="E5" s="13"/>
-      <c r="F5" s="7" t="s">
+      <c r="E5" s="24"/>
+      <c r="F5" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="I5" s="14"/>
-      <c r="J5" s="7" t="s">
+      <c r="I5" s="25"/>
+      <c r="J5" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="K5" s="13"/>
-      <c r="L5" s="9" t="s">
+      <c r="K5" s="24"/>
+      <c r="L5" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="M5" s="14"/>
-    </row>
-    <row r="6" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+      <c r="M5" s="25"/>
+    </row>
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.24" customHeight="true">
+      <c r="B6" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="I6" s="10" t="s">
+      <c r="I6" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="K6" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="L6" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="M6" s="19" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="9" t="s">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.24" customHeight="true">
+      <c r="B7" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="I7" s="23" t="s">
         <v>150</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="K7" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="L7" s="7" t="s">
+      <c r="L7" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="M7" s="12" t="s">
+      <c r="M7" s="23" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="9" t="s">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.24" customHeight="true">
+      <c r="B8" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="E8" s="13"/>
-      <c r="F8" s="7" t="s">
+      <c r="E8" s="24"/>
+      <c r="F8" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="G8" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="I8" s="13"/>
-      <c r="J8" s="7" t="s">
+      <c r="I8" s="24"/>
+      <c r="J8" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="K8" s="13"/>
-      <c r="L8" s="7" t="s">
+      <c r="K8" s="24"/>
+      <c r="L8" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="M8" s="13"/>
-    </row>
-    <row r="9" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="9" t="s">
+      <c r="M8" s="24"/>
+    </row>
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.24" customHeight="true">
+      <c r="B9" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="K9" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="L9" s="7" t="s">
+      <c r="L9" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="M9" s="8" t="s">
+      <c r="M9" s="19" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.24" customHeight="true">
+      <c r="B10" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="E10" s="11"/>
-      <c r="F10" s="9" t="s">
+      <c r="E10" s="22"/>
+      <c r="F10" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="I10" s="23" t="s">
         <v>155</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="J10" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="K10" s="12" t="s">
+      <c r="K10" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="L10" s="9" t="s">
+      <c r="L10" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="M10" s="11" t="s">
+      <c r="M10" s="22" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.24" customHeight="true">
+      <c r="B11" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="9" t="s">
+      <c r="C11" s="24"/>
+      <c r="D11" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="25" t="s">
         <v>157</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="G11" s="13" t="s">
+      <c r="G11" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="I11" s="13" t="s">
+      <c r="I11" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="J11" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="K11" s="13"/>
-      <c r="L11" s="7" t="s">
+      <c r="K11" s="24"/>
+      <c r="L11" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="M11" s="13" t="s">
+      <c r="M11" s="24" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7" t="s">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.24" customHeight="true">
+      <c r="B12" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="J12" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="K12" s="8" t="s">
+      <c r="K12" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="L12" s="7" t="s">
+      <c r="L12" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="M12" s="8" t="s">
+      <c r="M12" s="19" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="7" t="s">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.24" customHeight="true">
+      <c r="B13" s="18"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="7" t="s">
+      <c r="E13" s="23"/>
+      <c r="F13" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="G13" s="12" t="s">
+      <c r="G13" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="I13" s="12" t="s">
+      <c r="I13" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="J13" s="7" t="s">
+      <c r="J13" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="K13" s="12" t="s">
+      <c r="K13" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="L13" s="7" t="s">
+      <c r="L13" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="M13" s="12" t="s">
+      <c r="M13" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="55.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="7"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="7" t="s">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.24" customHeight="true">
+      <c r="B14" s="18"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="7" t="s">
+      <c r="E14" s="24"/>
+      <c r="F14" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="G14" s="13"/>
-      <c r="H14" s="7" t="s">
+      <c r="G14" s="24"/>
+      <c r="H14" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="I14" s="13"/>
-      <c r="J14" s="7" t="s">
+      <c r="I14" s="24"/>
+      <c r="J14" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="K14" s="13"/>
-      <c r="L14" s="7" t="s">
+      <c r="K14" s="24"/>
+      <c r="L14" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="M14" s="13"/>
+      <c r="M14" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3782,7 +3826,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="77"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/물레타령.xlsx
+++ b/sheets/민요/검수/물레타령.xlsx
@@ -3383,22 +3383,22 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="16" width="6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
-    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="51.95" customHeight="true">
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="48.19" customHeight="true">
       <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
@@ -3414,7 +3414,7 @@
       <c r="L2" s="17"/>
       <c r="M2" s="17"/>
     </row>
-    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.24" customHeight="true">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="71.62" customHeight="true">
       <c r="B3" s="18" t="s">
         <v>137</v>
       </c>
@@ -3452,7 +3452,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.24" customHeight="true">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="71.62" customHeight="true">
       <c r="B4" s="20" t="s">
         <v>117</v>
       </c>
@@ -3482,7 +3482,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.24" customHeight="true">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="71.62" customHeight="true">
       <c r="B5" s="18" t="s">
         <v>143</v>
       </c>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="M5" s="25"/>
     </row>
-    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.24" customHeight="true">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="71.62" customHeight="true">
       <c r="B6" s="18" t="s">
         <v>55</v>
       </c>
@@ -3550,7 +3550,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.24" customHeight="true">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="71.62" customHeight="true">
       <c r="B7" s="20" t="s">
         <v>143</v>
       </c>
@@ -3588,7 +3588,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.24" customHeight="true">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="71.62" customHeight="true">
       <c r="B8" s="20" t="s">
         <v>137</v>
       </c>
@@ -3618,7 +3618,7 @@
       </c>
       <c r="M8" s="24"/>
     </row>
-    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.24" customHeight="true">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="71.62" customHeight="true">
       <c r="B9" s="20" t="s">
         <v>132</v>
       </c>
@@ -3656,7 +3656,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.24" customHeight="true">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="71.62" customHeight="true">
       <c r="B10" s="18" t="s">
         <v>50</v>
       </c>
@@ -3692,7 +3692,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.24" customHeight="true">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="71.62" customHeight="true">
       <c r="B11" s="18" t="s">
         <v>54</v>
       </c>
@@ -3726,7 +3726,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.24" customHeight="true">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="71.62" customHeight="true">
       <c r="B12" s="18" t="s">
         <v>55</v>
       </c>
@@ -3764,7 +3764,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.24" customHeight="true">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="71.62" customHeight="true">
       <c r="B13" s="18"/>
       <c r="C13" s="23"/>
       <c r="D13" s="18" t="s">
@@ -3796,7 +3796,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.24" customHeight="true">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="71.62" customHeight="true">
       <c r="B14" s="18"/>
       <c r="C14" s="24"/>
       <c r="D14" s="18" t="s">
@@ -3826,7 +3826,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="77"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="83"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
